--- a/outputs/Продажи и остатки.xlsx
+++ b/outputs/Продажи и остатки.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ВСЕ ТОВАРЫ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="КОНЧИТСЯ ДО МАЯ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕТ ПРОДАЖ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЗАКОНЧИЛСЯ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СПРОС ПРОТИВ ОТГРУЗКИ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="КОНЧИТСЯ ДО МАЯ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕТ ПРОДАЖ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЗАКОНЧИЛСЯ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9074,6 +9075,239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Сезон</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Спрос, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Отгрузим, шт</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Не хватит, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>х1</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>11222</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>10336</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Октябрь 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>х1</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>11222</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>9390</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ноябрь 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>х1,5</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>16833</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>11129</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5704</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Декабрь 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>х2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>22444</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>12890</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>9554</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Январь 2027</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>х1</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>11222</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4560</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6662</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Февраль 2027</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>х2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>22444</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>8622</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>13822</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Март 2027</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>х1,5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>16833</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>10954</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Апрель 2027</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>х1</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>11222</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2837</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>8385</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr"/>
+      <c r="C10" s="10" t="n">
+        <v>123442</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>65644</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>57799</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13998,7 +14232,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14948,7 +15182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
